--- a/lite/ai.xlsx
+++ b/lite/ai.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11229"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/dev/python-for-excel-2e/src/lite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EB1163B-D548-414D-B027-225B754BD8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F544AD8-8F4A-C849-817A-945093689E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="780" windowWidth="33320" windowHeight="21360" xr2:uid="{6247F52B-40A5-F044-9DCE-1BA437C56878}"/>
   </bookViews>
@@ -611,7 +611,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="350" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -626,17 +626,26 @@
   <we:properties>
     <we:property name="main.py" value="&quot;import os\n\nfrom openai import AsyncOpenAI\nfrom xlwings import arg, func, ret\n\nMODEL = \&quot;gpt-5-chat-latest\&quot;\n\nclient = AsyncOpenAI(\n    api_key=os.environ[\&quot;OPENAI_API_KEY\&quot;],  # Read our environment variable\n    timeout=30,  # Some prompts take longer than the default timeout\n)\n\n\n@func\nasync def ai_models():\n    models = await client.models.list()\n    return [[m.id] for m in models.data]\n\n\n@func\n@ret(\&quot;json\&quot;)\n@arg(\&quot;*prompt\&quot;, \&quot;json\&quot;, ndim=\&quot;natural\&quot;)\nasync def ai(*prompt):\n    prompts = \&quot;\\n\\n\&quot;.join(prompt)\n    instructions = (\n        f\&quot;You are an Excel assistant. {prompts}\\n\\n\&quot;\n        \&quot;If required by the data, return a valid JSON 2D array without objects.\&quot;\n        \&quot;Do not include explanations, notes, or markdown formatting.\&quot;\n    )\n\n    # Use the Responses API\n    try:\n        response = await client.responses.create(\n            model=MODEL,\n            input=instructions,\n        )\n    except Exception as e:\n        return f\&quot;ERROR: {e}\&quot;\n\n    return response.output_text\n&quot;"/>
     <we:property name="pyodideVersion" value="&quot;0.27.5&quot;"/>
-    <we:property name="addinVersion" value="&quot;1.0.0.0-19&quot;"/>
-    <we:property name="requirements.txt" value="&quot;# Pin the version of packages that are installed from PyPI.\n# Don't pin the version if they are on this list:\n# https:\/\/pyodide.org\/en\/stable\/usage\/packages-in-pyodide.html\n#\n# New packages are installed on the fly.\n# However, the following situations require a restart:\n# - removing a package\n# - changing the version of a package\n# - adding an optional dependency of xlwings, e.g, polars\n\nxlwings==0.33.19  # required\npython-dotenv==1.2.1  # required\npyodide-http  # required\nblack  # required\nopenai&quot;"/>
+    <we:property name="addinVersion" value="&quot;1.0.0.0-35&quot;"/>
+    <we:property name="requirements.txt" value="&quot;# Pin the version of packages that are installed from PyPI.\n# Don't pin the version if they are on this list:\n# https:\/\/pyodide.org\/en\/stable\/usage\/packages-in-pyodide.html\n#\n# New packages are installed on the fly.\n# However, the following situations require a restart:\n# - removing a package\n# - changing the version of a package\n# - adding an optional dependency of xlwings, e.g, polars\n\nxlwings==0.33.20  # required\npython-dotenv==1.2.1  # required\npyodide-http  # required\nblack  # required\nopenai&quot;"/>
+    <we:property name="xlwingsWorkbookId" value="&quot;ee00e0a4-d29b-49b4-be69-13c6abec377b&quot;"/>
+    <we:property name="xlwingsSettingsWorkbook" value="&quot;{\&quot;startupBehavior\&quot;:\&quot;taskpane\&quot;}&quot;"/>
   </we:properties>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
   <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
     <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
       <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_WINGMAN</we:customFunctionIds>
         <we:customFunctionIds>_xldudf_AI</we:customFunctionIds>
         <we:customFunctionIds>_xldudf_AI_MODELS</we:customFunctionIds>
       </we:customFunctionIdList>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{0858819E-0033-43BF-8937-05EC82904868}">
+      <we:backgroundApp state="1" runtimeId="Taskpane.Url"/>
     </a:ext>
   </we:extLst>
 </we:webextension>
@@ -653,7 +662,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8524B3F-7E9C-7747-954D-114BE6697FA5}">
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23" style="3" bestFit="1" customWidth="1"/>
@@ -665,7 +674,7 @@
     <col min="7" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -681,95 +690,92 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="4"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="4"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="4"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="4"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="4"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="4"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="4"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="4"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="4"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="4"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="4"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="4"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="4"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>20</v>
       </c>
@@ -994,7 +1000,9 @@
       <c r="B53" s="4"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="4"/>
+      <c r="A54" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="B54" s="4"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
